--- a/artfynd/A 33890-2024 artfynd.xlsx
+++ b/artfynd/A 33890-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1633,6 +1633,121 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122782978</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Tolandsberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>782975</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7149202</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2018-07-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2018-07-09</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33890-2024 artfynd.xlsx
+++ b/artfynd/A 33890-2024 artfynd.xlsx
@@ -1638,7 +1638,7 @@
         <v>122782978</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
